--- a/artfynd/A 50079-2023 artfynd.xlsx
+++ b/artfynd/A 50079-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 50079-2023 artfynd.xlsx
+++ b/artfynd/A 50079-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,59 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>59529669</v>
+        <v>113018573</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>BispbergsFot, Dlr</t>
+          <t>Jätteklacken, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>545006.9194148843</v>
+        <v>544876</v>
       </c>
       <c r="R2" t="n">
-        <v>6690706.342295788</v>
+        <v>6690717</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +751,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2016-04-25</t>
+          <t>2023-10-30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>BLASIPPA</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +775,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Stig-Åke Svenson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Uno Skog</t>
+          <t>Stig-Åke Svenson, Åke Persson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>59529671</v>
+        <v>59529669</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,10 +829,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>545035.7373613755</v>
+        <v>545007</v>
       </c>
       <c r="R3" t="n">
-        <v>6690821.533945148</v>
+        <v>6690706</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,24 +862,14 @@
           <t>2016-04-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2016-04-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>BLASIPP-GRÄVD-LYA-ASP</t>
+          <t>BLASIPPA</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +896,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>59529675</v>
+        <v>59529670</v>
       </c>
       <c r="B4" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>545080.5486355539</v>
+        <v>545051</v>
       </c>
       <c r="R4" t="n">
-        <v>6690766.156830444</v>
+        <v>6690818</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,24 +964,14 @@
           <t>2016-04-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2016-04-25</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>BLA</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,15 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>59529670</v>
+        <v>59529671</v>
       </c>
       <c r="B5" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>545050.657723384</v>
+        <v>545036</v>
       </c>
       <c r="R5" t="n">
-        <v>6690817.758915315</v>
+        <v>6690822</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,24 +1066,14 @@
           <t>2016-04-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2016-04-25</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>BLA</t>
+          <t>BLASIPP-GRÄVD-LYA-ASP</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,6 +1097,414 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>59529673</v>
+      </c>
+      <c r="B6" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>BispbergsFot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>545045</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6690686</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>BLASIPPA-STIG</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>59529674</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>BispbergsFot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>545054</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6690694</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>BLASIPP</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>59529675</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>BispbergsFot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>545081</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6690766</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>59529676</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>BispbergsFot, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>545108</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6690792</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Säter</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2016-04-25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Uno Skog</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 50079-2023 artfynd.xlsx
+++ b/artfynd/A 50079-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113018573</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -893,6 +903,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529669</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529670</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529671</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1199,6 +1224,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529673</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1301,6 +1331,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529674</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1403,6 +1438,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529675</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1505,8 +1545,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59529676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>